--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.49.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.49.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.49.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.49.xlsx
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -595,14 +595,22 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: the fourth day from its date, that is, allowing two clearâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L35: symbol-only separator/garbage line :: 1850.</t>
@@ -610,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -659,16 +667,12 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pealed except as to the parts italicised in brackets :â€”</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: G</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -714,16 +718,12 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: It is orderedâ€”That the Master in ordinary of this Court</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: T</t>
+          <t>L49: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -770,7 +770,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 1846.</t>
+          <t>L110: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -817,7 +817,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: 181.</t>
+          <t>L124: symbol-only separator/garbage line :: 1846.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -864,7 +864,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: T</t>
+          <t>L125: symbol-only separator/garbage line :: 181.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -909,7 +909,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L146: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -969,12 +973,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1047,7 +1051,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
